--- a/光伏配储项目/电价数据/2026/莲花站.xlsx
+++ b/光伏配储项目/电价数据/2026/莲花站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55359</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.51509</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8570800000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.12477</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.01685</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.9138200000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.71305</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.72262</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.58823</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.52166</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.6845800000000001</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.6847000000000001</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.67502</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.51495</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.70235</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.6926599999999999</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.65564</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.68113</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.52419</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.69547</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.54375</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.69353</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.70135</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.54852</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.72638</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.81589</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.85723</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.67614</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6713300000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.73309</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.75578</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.00878</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.6971799999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.78326</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9487599999999999</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31127</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52281</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7590399999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76693</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74688</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9270900000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.89371</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04702</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.31399</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.12073</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.11829</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.73365</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.20889</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.16815</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09643</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22781</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.5343</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.1024</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24625</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47549</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.30402</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.2353</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.79844</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.40966</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35327</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.2839</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8028999999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16736</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03677</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17624</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51247</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.6116200000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.58593</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.49062</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48399</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.51934</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.51127</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.51124</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.50102</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.50752</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.5562999999999999</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.76471</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.0687</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.83735</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.58928</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48296</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45612</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.93426</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.15008</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.77518</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.11941</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03692</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.98582</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7072200000000001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5476599999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.56649</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.67908</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.15253</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.23004</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47392</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15713</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.07805</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.81724</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.25034</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13497</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28275</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6215000000000001</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63793</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5699299999999999</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62175</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.15953</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16738</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17606</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17065</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9674199999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18768</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20249</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66867</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.16047</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20552</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.20904</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.5053</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.41011</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16677</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50953</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26392</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74276</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76485</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91537</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.60154</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.68203</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6919099999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.53171</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.50643</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.8331799999999999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.59305</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.5850599999999999</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.55377</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.55544</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.63146</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48463</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48648</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.5738799999999999</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.5226000000000001</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.5551799999999999</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49361</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.4959</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.50603</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.69235</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8304400000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10756</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.87352</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.74417</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.7028</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60427</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6429400000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42514</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.72866</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16373</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.52068</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6764199999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16606</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.61963</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18745</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.16412</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.79232</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.93862</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16293</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.16439</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8917200000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.55937</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47457</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67406</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16479</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.0277</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.16351</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.39143</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23448</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16484</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21545</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20929</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26807</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28507</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64779</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.17013</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17303</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78201</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.0381</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.0776</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09847</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.08454</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20346</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16733</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24729</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.99405</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75379</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.71033</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5299199999999999</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.10827</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.71949</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.71278</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.18853</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6779700000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.8521299999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.5386599999999999</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.59222</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.20961</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.5900599999999999</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.52195</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.65151</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.5234500000000001</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.51474</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.40861</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.51961</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.5742999999999999</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.49278</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.49252</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.45776</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48902</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.67601</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.7180700000000001</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93237</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16688</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30812</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8372200000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55051</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.6656</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9032899999999999</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8637</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16314</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43948</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77238</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.95214</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20353</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.6885</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.1225</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5221399999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48499</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.65374</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.99518</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10178</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.2485</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16748</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.05989</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.98072</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02538</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.98933</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.25037</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.43995</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.7924099999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34753</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.20947</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.18986</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07307</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.16005</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12113</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15288</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.25372</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31725</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15292</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26855</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18719</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18583</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18764</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18797</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17348</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.15105</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17552</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72329</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.52244</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.72548</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32161</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74341</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49339</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47746</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50431</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52273</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45515</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.71601</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.84724</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61442</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70121</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.72625</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8447899999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.7047</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55038</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54943</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.53816</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59197</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47029</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08479</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26791</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5497000000000001</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48186</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51178</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.63266</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48279</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48293</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.4871</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.59382</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.50517</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50562</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40864</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48581</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34388</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.19006</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.96501</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9808600000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.58999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.64551</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.54259</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.5266900000000001</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.54142</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.50893</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.6814199999999999</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.52476</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.52506</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.50762</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.50847</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.5092300000000001</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07331</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04531</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08278000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12862</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04709000000000001</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04676</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04593</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04667</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04633</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25277</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27606</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44582</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.59063</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.5363300000000001</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.55838</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.53815</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.53737</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55467</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.26978</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7409199999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8735000000000001</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.6740499999999999</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6480199999999999</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6669299999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7479199999999999</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.93851</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48057</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.72942</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73107</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.8870800000000001</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.63039</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48242</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44883</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08518000000000001</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73117</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72753</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6382599999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6025700000000001</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.72815</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.78859</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78244</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.60004</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7413200000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01764</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40535</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8425199999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.43307</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29615</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.7879400000000001</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.37982</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04435</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.79976</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.40008</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.7646</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44325</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.77396</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80037</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7850199999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87879</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50196</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41136</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46008</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21847</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54122</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.61422</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.58162</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.5617300000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.5704</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.5770599999999999</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.50581</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.5786100000000001</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.55816</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.4672</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.49074</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.5394099999999999</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.5112300000000001</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.5149199999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.51151</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.51145</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.54735</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.5124500000000001</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.56411</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.46917</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.56762</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.49076</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56364</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6662100000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07973</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.63827</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50244</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.56901</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59874</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00115</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33888</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30649</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27483</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5591900000000001</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8017799999999999</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5728799999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6506799999999999</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5503400000000001</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.9553400000000001</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.77623</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72534</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64183</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57511</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.9879600000000001</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.9285399999999999</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78646</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.54137</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.66996</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.58736</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.6213200000000001</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.66204</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.70178</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.63913</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.6606799999999999</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58236</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.65866</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.67503</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.6206699999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.66872</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.68724</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7605299999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.67789</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.7572000000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.68713</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.68474</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.68635</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.67047</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.6600499999999999</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.6175499999999999</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.6592</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.60201</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.54049</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.55325</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5782200000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.5547300000000001</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.53998</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.5295800000000001</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46655</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5737100000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.60537</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6194</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6774</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.5460900000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.49812</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.52235</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.49076</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64101</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.5124500000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.61729</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.72702</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.8704700000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.11036</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.93183</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.54455</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11298</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84288</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.85846</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.63927</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.80899</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06651</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.56741</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52206</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.8741599999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.99203</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.53459</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.18925</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.7830199999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8126100000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.73807</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.73911</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44317</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51244</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.79283</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43547</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7484</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.1653</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9209700000000001</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64266</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.66452</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7002699999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55423</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16359</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61167</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90883</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.57614</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.57081</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.33318</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.25772</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.22554</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.33386</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.00492</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.51831</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.60164</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.85858</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50503</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.74983</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.0751</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07302</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.90544</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.98239</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.93602</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17361</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15326</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.86168</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15457</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60691</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9697100000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01497</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.15396</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9495399999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.9897899999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58392</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.9233300000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.98064</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.0882</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.8847200000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.8723500000000001</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79274</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09562</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55401</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.95914</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.99026</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74281</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33156</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.60488</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.48815</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.5480900000000001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.58748</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.49729</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.47781</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.4868</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.52977</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8330599999999999</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71421</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.5456799999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.5655800000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.7220700000000001</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.84964</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.56775</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.57192</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.57369</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.50849</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.5555800000000001</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.6147</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.5575399999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.56765</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.45137</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.45753</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6768500000000001</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54043</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.50858</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.51036</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.50722</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5676599999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.44736</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.46813</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.56847</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.5258999999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.5325299999999999</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.51962</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.54627</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.48989</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.51261</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.43764</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.5201399999999999</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.5215299999999999</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.48326</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.47052</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45345</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55398</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.46998</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48509</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7010700000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6028600000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62773</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8490700000000001</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27159</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16649</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85226</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70145</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.94031</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16806</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12176</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01864</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54189</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44597</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41321</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42489</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56313</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.45999</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.45711</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.50087</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43598</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.50571</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.71508</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.05232</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41361</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.11085</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.99086</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.97958</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98112</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56599</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54705</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94637</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.0863</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78405</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01332</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76805</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64862</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64136</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70866</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80011</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29858</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.90612</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.49588</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.6287999999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.28992</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.11654</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.78492</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62406</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.6577</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67107</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66614</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64311</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66761</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20689</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70053</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78233</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.69784</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70562</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71378</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63333</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74807</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02176</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13156</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69168</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70012</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69389</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77352</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72368</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8130700000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6664800000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46301</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.06266</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.46461</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.57789</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.48767</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34413</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.59785</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17431</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.49861</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.48856</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.46169</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.50668</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.4991</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.49404</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.74698</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49506</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51068</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51891</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40652</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92228</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47469</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17959</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.9023300000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76325</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49751</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48989</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44866</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74658</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42618</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51506</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68058</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49591</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40556</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42696</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66465</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6517999999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8316399999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.52155</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48661</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.48169</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.69875</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.46999</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.43999</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54608</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76154</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76824</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.47991</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54665</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50163</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72324</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76267</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55428</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50187</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02062</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48738</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44702</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09498</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12991</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08389</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11241</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12888</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01866</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19446</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14273</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13194</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17431</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84137</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19132</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84846</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34121</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90389</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73404</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.7577999999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9490700000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.66869</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.38995</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.54911</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.54072</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.52967</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.53444</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.46405</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7559900000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.37087</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.34834</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42729</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.61242</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.6067899999999999</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.52849</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.5108</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.57392</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.58969</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.5907</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.51571</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.58484</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.53046</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.57389</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.50397</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46859</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46854</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.50207</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49864</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.63719</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54726</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.49881</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53707</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.02518</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.7728</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74068</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27928</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34078</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71718</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.6407</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34733</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99451</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59116</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.4929</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49443</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.53899</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.58947</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73288</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17626</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.6905800000000001</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.91169</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6642899999999999</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93333</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.8797999999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.7443</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71357</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17517</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17635</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.42443</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23548</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.61497</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20345</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28244</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07609</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.39777</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.66498</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.63598</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43034</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.13596</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6324099999999999</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47279</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.50442</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44888</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48278</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53185</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.8007799999999999</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.66801</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.64918</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50871</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.06751</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66594</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66326</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.79575</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04799</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.16646</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49944</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19208</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54599</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15313</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5567000000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5717300000000001</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49754</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23462</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47867</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4592</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50068</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51129</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43137</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.53818</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5153</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.59685</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7562300000000001</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12724</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.68702</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.55164</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45836</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43167</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49282</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44755</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58033</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.4774</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44794</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46199</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44884</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46309</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.54516</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.49199</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.49858</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.46026</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.36966</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.85976</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.48222</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.44185</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.43043</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.43012</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23335</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.69855</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17238</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.25975</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09739</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.68811</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5585399999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49154</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48415</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.0929</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.3654</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.8442499999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.80299</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52158</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75295</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75154</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51179</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42682</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55404</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44183</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.50852</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.73656</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.57085</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45256</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7527999999999999</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.5225700000000001</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28371</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.28707</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21642</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06069</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.95338</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28347</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.61038</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54425</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49111</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5751799999999999</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5457799999999999</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5409299999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21331</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.7524500000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.7509</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5748799999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44801</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49159</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.9847100000000001</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.75912</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61807</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.75005</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17187</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60053</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.7264299999999999</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62375</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.23566</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.8726799999999999</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.8581599999999999</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.87967</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.89827</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15224</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.63847</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9308500000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.67848</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.95582</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.61865</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.63675</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.73515</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.61913</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79126</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24326</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03373</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.9949600000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.00747</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51359</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.3402</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04777</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7537699999999999</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34523</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55672</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8010700000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.54962</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75073</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7525299999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5589400000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46877</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45843</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40699</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41901</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42647</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62725</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59017</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.55622</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5372400000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49444</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5570700000000001</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8113899999999999</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.15295</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11881</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03171</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12152</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72506</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.71982</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04255</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06092</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.66799</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55548</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5619500000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47714</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54627</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5514199999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54095</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65698</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54125</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04308</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.65387</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5465399999999999</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49691</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49745</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48048</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49746</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48026</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57465</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5549500000000001</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55845</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49588</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5115500000000001</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49832</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.55829</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.65696</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15176</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.0547</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6581900000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.57982</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15044</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.86334</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.65744</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.13959</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.81226</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49228</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5095500000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49706</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53277</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34433</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.7064400000000001</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.5790700000000001</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.58562</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.7209500000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.54834</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41883</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6256499999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58321</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.62928</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00399</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17379</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92401</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.96063</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.00963</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.95065</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.91698</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.94686</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9307799999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.91411</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.91643</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.66895</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.02315</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.66774</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.02007</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.12236</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10422</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.69814</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.9211</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8419800000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.90887</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54153</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66613</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68861</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73701</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78708</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.19649</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.0766</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.01611</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.3287</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01177</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11085</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.9152100000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7513500000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.75061</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8130599999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69138</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69071</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5560499999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.68821</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7241799999999999</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6845399999999999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7466</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6946599999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46087</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.73263</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5196000000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50532</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.99363</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.89071</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00702</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.89534</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01484</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.9976699999999999</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.99786</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.16165</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06706</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.08828</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.66515</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5948300000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71746</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.70459</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02572</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69727</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.75029</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13447</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.22868</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.42938</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.19789</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.3599</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.39782</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.37709</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.74068</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.65143</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.41893</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.42075</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80732</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.75485</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.8017799999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.55689</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7539</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43938</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8110499999999999</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31364</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00406</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9341799999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.96041</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03392</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16256</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06188</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86441</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69348</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22239</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20862</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.20926</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15197</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86771</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70363</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09735</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10824</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10827</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13454</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10598</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52066</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20129</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.63973</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57751</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.73115</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.66335</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18531</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8617400000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06617</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03237</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.04961</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03629</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06925</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12828</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05072</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06133</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18427</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16281</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21637</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20342</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26589</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16952</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14288</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12013</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10077</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12692</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17663</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19422</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.1748</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07635</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.67377</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.61437</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5655399999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.54818</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53063</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31374</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31094</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06784</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47908</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5198700000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44245</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43328</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43216</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43264</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.42102</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84836</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.68363</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.6992699999999999</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.6509199999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.94116</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.75215</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.94652</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15827</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30607</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44514</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43327</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45953</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54544</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.2521</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85122</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.61978</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7333999999999999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70063</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50286</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84435</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.86627</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.2144</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.7732100000000001</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57996</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.5805399999999999</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62697</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.70735</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.5829299999999999</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7350399999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.60999</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.19969</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17633</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41124</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17769</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17854</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18378</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10337</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07811</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20745</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10582</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19213</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05069</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08223</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20652</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08223</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54225</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80736</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8041200000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5640299999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.2134</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84912</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84962</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55457</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539400000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49921</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54779</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5203099999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55759</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17565</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88301</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49397</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17089</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50944</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5694400000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8441900000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59699</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8529099999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5229199999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5436799999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17766</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55536</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17376</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54925</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5503899999999999</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5807899999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79962</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5550900000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79915</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8491000000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17424</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7987000000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6835599999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05156</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.1749</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17593</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.1773</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17522</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82421</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73249</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6450900000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.67665</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.68465</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7311299999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8348300000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81804</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6152799999999999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.80668</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7563799999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13666</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.7506499999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60946</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63624</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.63834</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.61722</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61456</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7036100000000001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67059</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.81362</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70408</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
